--- a/grupos/5BLCM - Estadisticos 20211.xlsx
+++ b/grupos/5BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,18 +188,18 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
@@ -221,220 +221,220 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO</t>
+  </si>
+  <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
   </si>
   <si>
     <t>NARVAEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>TLEHUACTLE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
+  </si>
+  <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
   </si>
   <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>GUILLERMO UBALDO</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>ASAEL PAULINO</t>
@@ -971,13 +971,13 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1048,13 +1048,13 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1125,13 +1125,13 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1202,13 +1202,13 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1279,13 +1279,13 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1315,10 +1315,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1356,13 +1356,13 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1407,7 +1407,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1433,13 +1433,13 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1510,13 +1510,13 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1546,10 +1546,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1587,13 +1587,13 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1638,7 +1638,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1664,13 +1664,13 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1679,7 +1679,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1700,10 +1700,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1741,13 +1741,13 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1818,13 +1818,13 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1833,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1869,7 +1869,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1895,13 +1895,13 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1946,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1960,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -1972,13 +1972,13 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2049,13 +2049,13 @@
         <v>4</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2085,10 +2085,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2100,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2126,13 +2126,13 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2177,7 +2177,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2203,13 +2203,13 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2218,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2242,7 +2242,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2254,7 +2254,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2280,13 +2280,13 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2331,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2357,13 +2357,13 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2393,13 +2393,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2434,13 +2434,13 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2470,10 +2470,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2485,7 +2485,7 @@
         <v>-1</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2499,7 +2499,7 @@
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2547,13 +2547,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2562,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2588,13 +2588,13 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2665,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2680,7 +2680,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2742,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2819,13 +2819,13 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2855,13 +2855,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2896,13 +2896,13 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2911,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2932,13 +2932,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2973,13 +2973,13 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3032,13 +3032,13 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>-1</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -3050,13 +3050,13 @@
         <v>4</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3086,13 +3086,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3127,13 +3127,13 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3142,7 +3142,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3204,13 +3204,13 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3240,13 +3240,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>9</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3281,13 +3281,13 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3296,7 +3296,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3320,7 +3320,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3358,13 +3358,13 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3373,7 +3373,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3400,7 +3400,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3435,13 +3435,13 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3450,7 +3450,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3512,13 +3512,13 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3548,10 +3548,10 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3563,7 +3563,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3660,30 +3660,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>94.12</v>
+      </c>
+      <c r="G3">
+        <v>5.88</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>11.76</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3692,30 +3692,30 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="G4">
-        <v>8.82</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3724,30 +3724,30 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G5">
         <v>2.94</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3756,19 +3756,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G6">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3791,22 +3791,22 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>97.06</v>
       </c>
       <c r="G7">
+        <v>2.94</v>
+      </c>
+      <c r="H7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3851,10 +3851,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3871,10 +3871,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3885,36 +3885,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920200</v>
+        <v>19330051920202</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920202</v>
+        <v>19330051920207</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3925,36 +3925,36 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920202</v>
+        <v>19330051920213</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920207</v>
+        <v>19330051920217</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3965,122 +3965,22 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920209</v>
+        <v>19330051920217</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920213</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920217</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920217</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920217</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920217</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4119,47 +4019,47 @@
         <v>19330051920217</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920202</v>
+        <v>19330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920195</v>
+        <v>19330051920197</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4167,16 +4067,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920197</v>
+        <v>19330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4184,16 +4084,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920200</v>
+        <v>19330051920207</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4201,16 +4101,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920207</v>
+        <v>19330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4218,47 +4118,47 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920209</v>
+        <v>19330051920186</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920213</v>
+        <v>19330051920185</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920186</v>
+        <v>19330051920187</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4269,13 +4169,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920185</v>
+        <v>19330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4286,13 +4186,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920187</v>
+        <v>19330051920190</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4303,13 +4203,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920189</v>
+        <v>19330051920192</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4320,13 +4220,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920190</v>
+        <v>19330051920194</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4337,13 +4237,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920192</v>
+        <v>19330051920193</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4354,13 +4254,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920194</v>
+        <v>19330051920196</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4371,13 +4271,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920193</v>
+        <v>19330051920198</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4388,16 +4288,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920196</v>
+        <v>19330051920199</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4405,16 +4305,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920198</v>
+        <v>19330051920200</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4422,16 +4322,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920199</v>
+        <v>19330051920201</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4439,13 +4339,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920201</v>
+        <v>19330051920203</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4456,13 +4356,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920203</v>
+        <v>19330051920204</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4473,13 +4373,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920204</v>
+        <v>19330051920206</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4490,13 +4390,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920206</v>
+        <v>19330051920209</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4510,10 +4410,10 @@
         <v>19330051920211</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4527,7 +4427,7 @@
         <v>19330051920215</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>66</v>
@@ -4544,7 +4444,7 @@
         <v>19330051920212</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
         <v>66</v>
@@ -4561,10 +4461,10 @@
         <v>19330051920214</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4578,10 +4478,10 @@
         <v>19330051920216</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4595,10 +4495,10 @@
         <v>19330051920218</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4612,10 +4512,10 @@
         <v>19330051920220</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4629,10 +4529,10 @@
         <v>19330051920439</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4646,10 +4546,10 @@
         <v>19330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4663,10 +4563,10 @@
         <v>19330051920221</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4680,10 +4580,10 @@
         <v>18330051920351</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4699,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4731,68 +4631,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920195</v>
+        <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
         <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920202</v>
+        <v>19330051920195</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4800,16 +4700,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920202</v>
+        <v>19330051920197</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4823,16 +4723,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920197</v>
+        <v>19330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -4846,93 +4746,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920200</v>
+        <v>19330051920213</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920201</v>
-      </c>
-      <c r="B8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920209</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920213</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20211.xlsx
+++ b/grupos/5BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
@@ -215,22 +215,115 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO</t>
+  </si>
+  <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUILLEN</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
   </si>
   <si>
     <t>LINARES</t>
@@ -239,16 +332,70 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
   </si>
   <si>
     <t>EDITH</t>
@@ -257,193 +404,46 @@
     <t>KEVIN JETHZAEL</t>
   </si>
   <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
     <t>DANNA PAOLA</t>
   </si>
   <si>
+    <t>GUILLERMO UBALDO</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
   </si>
   <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>ASAEL PAULINO</t>
+  </si>
+  <si>
+    <t>HEIDI YAMILET</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
     <t>JANETH</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ASAEL PAULINO</t>
-  </si>
-  <si>
-    <t>HEIDI YAMILET</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
   <si>
     <t>JUDITH ESTEFANIA</t>
@@ -983,7 +983,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1060,7 +1060,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1137,7 +1137,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1291,7 +1291,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1368,7 +1368,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1404,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1445,7 +1445,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1522,7 +1522,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1581,7 +1581,7 @@
         <v>7</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -1599,7 +1599,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1676,7 +1676,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1735,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1753,7 +1753,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1830,7 +1830,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1907,7 +1907,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -2097,7 +2097,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2120,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -2174,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2292,7 +2292,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2328,7 +2328,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2369,7 +2369,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>7</v>
@@ -2446,7 +2446,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2482,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2523,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2600,7 +2600,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2754,7 +2754,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2813,7 +2813,7 @@
         <v>6</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2831,7 +2831,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2908,7 +2908,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -2985,7 +2985,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -3216,7 +3216,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3293,7 +3293,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3370,7 +3370,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3483,7 +3483,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3628,30 +3628,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3660,25 +3660,25 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G3">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3845,141 +3845,41 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920195</v>
+        <v>19330051920217</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920197</v>
+        <v>19330051920217</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
         <v>66</v>
       </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920202</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920207</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920213</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920217</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920217</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4019,13 +3919,13 @@
         <v>19330051920217</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4033,98 +3933,98 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>19330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920197</v>
+        <v>19330051920185</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920202</v>
+        <v>19330051920187</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920207</v>
+        <v>19330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920213</v>
+        <v>19330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920186</v>
+        <v>19330051920192</v>
       </c>
       <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
         <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -4135,13 +4035,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920185</v>
+        <v>19330051920194</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
         <v>124</v>
@@ -4152,13 +4052,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920187</v>
+        <v>19330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4169,13 +4069,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920189</v>
+        <v>19330051920195</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4186,13 +4086,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920190</v>
+        <v>19330051920197</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4203,13 +4103,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920192</v>
+        <v>19330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4220,13 +4120,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920194</v>
+        <v>19330051920198</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4237,16 +4137,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920193</v>
+        <v>19330051920199</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4254,16 +4154,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920196</v>
+        <v>19330051920200</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4271,16 +4171,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920198</v>
+        <v>19330051920201</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4288,16 +4188,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920199</v>
+        <v>19330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4305,13 +4205,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920200</v>
+        <v>19330051920203</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4322,13 +4222,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920201</v>
+        <v>19330051920204</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4339,13 +4239,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920203</v>
+        <v>19330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4356,13 +4256,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920204</v>
+        <v>19330051920207</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4373,13 +4273,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920206</v>
+        <v>19330051920209</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4390,13 +4290,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920209</v>
+        <v>19330051920211</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4407,13 +4307,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920211</v>
+        <v>19330051920215</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4424,13 +4324,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920215</v>
+        <v>19330051920212</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4441,13 +4341,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920212</v>
+        <v>19330051920213</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4461,10 +4361,10 @@
         <v>19330051920214</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4478,10 +4378,10 @@
         <v>19330051920216</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4495,10 +4395,10 @@
         <v>19330051920218</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4512,10 +4412,10 @@
         <v>19330051920220</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4529,10 +4429,10 @@
         <v>19330051920439</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4546,10 +4446,10 @@
         <v>19330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4563,10 +4463,10 @@
         <v>19330051920221</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4580,10 +4480,10 @@
         <v>18330051920351</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4599,7 +4499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4634,137 +4534,22 @@
         <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920195</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920197</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920202</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920213</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5BLCM - Estadisticos 20211.xlsx
+++ b/grupos/5BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1288,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1365,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1442,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1555,7 +1555,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1596,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1904,7 +1904,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1981,7 +1981,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2058,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2135,7 +2135,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2212,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2248,7 +2248,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2289,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2325,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2366,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2443,7 +2443,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2520,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -2633,7 +2633,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2674,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2828,7 +2828,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -2864,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2905,7 +2905,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -2982,7 +2982,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3213,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3290,7 +3290,7 @@
         <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3367,7 +3367,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3403,7 +3403,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3444,7 +3444,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -3480,7 +3480,7 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3521,7 +3521,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3628,16 +3628,16 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G2">
-        <v>5.88</v>
+        <v>11.76</v>
       </c>
       <c r="H2">
         <v>7.6</v>
@@ -4499,7 +4499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4531,16 +4531,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920207</v>
+        <v>19330051920201</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4549,6 +4549,52 @@
         <v>55</v>
       </c>
       <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920207</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20211.xlsx
+++ b/grupos/5BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,199 +215,199 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>CERON</t>
   </si>
   <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
     <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -989,22 +989,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1066,22 +1066,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1143,22 +1143,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1220,22 +1220,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1297,22 +1297,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1374,22 +1374,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1451,22 +1451,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1528,31 +1528,31 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1605,22 +1605,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1635,10 +1635,10 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1682,22 +1682,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1759,28 +1759,28 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1789,7 +1789,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1836,28 +1836,28 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1913,28 +1913,28 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1946,7 +1946,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1990,22 +1990,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2067,22 +2067,22 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2144,40 +2144,40 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2215,43 +2215,43 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2298,28 +2298,28 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2328,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2375,28 +2375,28 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2405,10 +2405,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2452,22 +2452,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2476,16 +2476,16 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2529,22 +2529,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2562,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2606,22 +2606,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2683,28 +2683,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2760,28 +2760,28 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2837,37 +2837,37 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2914,40 +2914,40 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2991,22 +2991,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3035,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -3044,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -3053,7 +3053,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -3062,34 +3062,34 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3145,28 +3145,28 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3222,22 +3222,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3299,22 +3299,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3376,22 +3376,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3453,22 +3453,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3530,28 +3530,28 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3560,10 +3560,10 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3663,27 +3663,27 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>97.06</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3695,27 +3695,27 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>97.06</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3736,7 +3736,7 @@
         <v>2.94</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3768,7 +3768,7 @@
         <v>2.94</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3788,19 +3788,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3841,46 +3841,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920217</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920217</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3916,30 +3876,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920217</v>
+        <v>19330051920186</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920186</v>
+        <v>19330051920185</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>118</v>
@@ -3950,13 +3910,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920185</v>
+        <v>19330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>119</v>
@@ -3967,13 +3927,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920187</v>
+        <v>19330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>120</v>
@@ -3984,13 +3944,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920189</v>
+        <v>19330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
         <v>121</v>
@@ -4001,13 +3961,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920190</v>
+        <v>19330051920192</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>122</v>
@@ -4018,13 +3978,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920192</v>
+        <v>19330051920194</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -4035,13 +3995,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920194</v>
+        <v>19330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>124</v>
@@ -4052,13 +4012,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920193</v>
+        <v>19330051920195</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4069,13 +4029,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920195</v>
+        <v>19330051920197</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4086,13 +4046,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920197</v>
+        <v>19330051920196</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4103,13 +4063,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920196</v>
+        <v>19330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4120,13 +4080,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920198</v>
+        <v>19330051920199</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4137,16 +4097,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920199</v>
+        <v>19330051920200</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4154,16 +4114,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920200</v>
+        <v>19330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4171,16 +4131,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920201</v>
+        <v>19330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4188,16 +4148,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920202</v>
+        <v>19330051920203</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4205,16 +4165,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920203</v>
+        <v>19330051920204</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4222,16 +4182,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920204</v>
+        <v>19330051920206</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4239,16 +4199,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920206</v>
+        <v>19330051920207</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4256,16 +4216,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920207</v>
+        <v>19330051920209</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4273,16 +4233,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920209</v>
+        <v>19330051920211</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4290,16 +4250,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920211</v>
+        <v>19330051920215</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4307,16 +4267,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920215</v>
+        <v>19330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4324,16 +4284,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920212</v>
+        <v>19330051920213</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4341,16 +4301,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920213</v>
+        <v>19330051920214</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4358,16 +4318,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920214</v>
+        <v>19330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4375,16 +4335,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920216</v>
+        <v>19330051920217</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4395,10 +4355,10 @@
         <v>19330051920218</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4412,10 +4372,10 @@
         <v>19330051920220</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4429,10 +4389,10 @@
         <v>19330051920439</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4446,10 +4406,10 @@
         <v>19330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4463,10 +4423,10 @@
         <v>19330051920221</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4480,10 +4440,10 @@
         <v>18330051920351</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4534,10 +4494,10 @@
         <v>19330051920201</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
         <v>131</v>
@@ -4557,10 +4517,10 @@
         <v>19330051920203</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>133</v>
@@ -4580,10 +4540,10 @@
         <v>19330051920207</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>

--- a/grupos/5BLCM - Estadisticos 20211.xlsx
+++ b/grupos/5BLCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1075,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1324,7 +1324,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1460,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1537,7 +1537,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1555,7 +1555,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1691,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1786,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1845,7 +1845,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1922,7 +1922,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -1940,7 +1940,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -2017,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2076,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2153,7 +2153,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2307,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2325,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2384,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -2461,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2538,7 +2538,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2615,7 +2615,7 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2769,7 +2769,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2923,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -3000,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -3059,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -3077,7 +3077,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3154,7 +3154,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3172,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3462,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -3539,7 +3539,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -3557,7 +3557,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3628,19 +3628,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G2">
-        <v>11.76</v>
+        <v>8.82</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4459,7 +4459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4491,16 +4491,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920201</v>
+        <v>19330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4514,16 +4514,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920203</v>
+        <v>19330051920204</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4532,29 +4532,6 @@
         <v>55</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>
